--- a/data/trans_camb/P3A_R-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P3A_R-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,72; 29,38</t>
+          <t>-0,24; 30,66</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-16,98; 15,11</t>
+          <t>-18,04; 13,52</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,46; 48,98</t>
+          <t>7,45; 48,25</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-14,76; 14,77</t>
+          <t>-16,44; 15,64</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-31,6; -1,35</t>
+          <t>-31,24; -0,23</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,83; 38,61</t>
+          <t>7,75; 38,82</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,31; 18,23</t>
+          <t>-2,96; 18,9</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-20,59; 1,9</t>
+          <t>-19,29; 2,04</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>14,9; 39,81</t>
+          <t>14,0; 38,92</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,19; 93,02</t>
+          <t>-1,71; 101,69</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-37,12; 47,65</t>
+          <t>-40,4; 43,7</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18,78; 158,23</t>
+          <t>18,08; 151,89</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-27,79; 37,47</t>
+          <t>-27,52; 38,64</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-56,43; -2,4</t>
+          <t>-55,27; 1,66</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,36; 97,81</t>
+          <t>14,1; 100,36</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-4,66; 48,02</t>
+          <t>-5,36; 51,67</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-42,36; 6,72</t>
+          <t>-40,73; 5,5</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>31,38; 105,84</t>
+          <t>30,31; 103,05</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-8,8; 3,31</t>
+          <t>-8,47; 3,84</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,94; 4,18</t>
+          <t>-7,96; 4,36</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>43,49; 54,7</t>
+          <t>44,2; 55,2</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-11,33; 0,73</t>
+          <t>-10,8; 0,94</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-10,2; 1,66</t>
+          <t>-9,63; 2,57</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>42,56; 52,23</t>
+          <t>42,47; 52,49</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-7,96; 0,59</t>
+          <t>-8,01; 0,56</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-7,2; 1,7</t>
+          <t>-7,16; 1,26</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>44,52; 52,24</t>
+          <t>44,66; 52,12</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-21,92; 9,81</t>
+          <t>-21,06; 11,24</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-19,66; 12,05</t>
+          <t>-19,85; 12,8</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>102,89; 163,71</t>
+          <t>106,78; 166,07</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-26,95; 2,4</t>
+          <t>-26,13; 2,67</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-24,4; 4,78</t>
+          <t>-23,11; 7,32</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>100,24; 148,45</t>
+          <t>99,01; 148,53</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-19,87; 1,61</t>
+          <t>-20,11; 1,57</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-17,86; 4,78</t>
+          <t>-18,16; 3,47</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>109,15; 148,25</t>
+          <t>109,16; 146,82</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-14,35; 4,08</t>
+          <t>-14,51; 3,68</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-13,5; 2,82</t>
+          <t>-13,47; 4,54</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>51,92; 67,71</t>
+          <t>52,53; 67,67</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,06; 14,97</t>
+          <t>-3,16; 14,67</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 15,86</t>
+          <t>-1,95; 15,01</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>60,31; 74,94</t>
+          <t>61,71; 75,61</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-5,51; 8,35</t>
+          <t>-5,77; 6,87</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-6,16; 6,57</t>
+          <t>-5,65; 6,89</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>58,79; 69,42</t>
+          <t>57,99; 68,72</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-43,08; 16,97</t>
+          <t>-43,27; 15,2</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-40,89; 9,93</t>
+          <t>-40,39; 17,58</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>149,28; 293,82</t>
+          <t>149,98; 294,27</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-13,35; 85,76</t>
+          <t>-12,12; 81,99</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-8,46; 91,12</t>
+          <t>-7,15; 87,77</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>212,41; 447,38</t>
+          <t>220,87; 465,83</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-19,63; 39,39</t>
+          <t>-19,71; 31,85</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-20,75; 28,78</t>
+          <t>-19,12; 30,93</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>197,31; 328,01</t>
+          <t>193,44; 311,44</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-5,59; 4,2</t>
+          <t>-5,96; 4,02</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-7,89; 1,52</t>
+          <t>-7,44; 2,15</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>45,46; 54,99</t>
+          <t>46,16; 54,95</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-7,64; 2,28</t>
+          <t>-7,0; 2,52</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-7,6; 1,71</t>
+          <t>-7,09; 2,08</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>46,15; 54,12</t>
+          <t>46,52; 54,27</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-5,01; 1,99</t>
+          <t>-4,86; 1,97</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-5,93; 0,69</t>
+          <t>-6,07; 0,52</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>47,51; 53,24</t>
+          <t>47,25; 53,52</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-14,93; 12,82</t>
+          <t>-15,9; 11,94</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-21,13; 4,43</t>
+          <t>-20,07; 6,49</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>117,83; 169,14</t>
+          <t>120,3; 168,85</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-20,19; 6,92</t>
+          <t>-18,68; 7,94</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-19,78; 5,34</t>
+          <t>-18,7; 6,28</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>118,28; 165,08</t>
+          <t>121,04; 166,46</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-13,32; 6,01</t>
+          <t>-12,96; 5,72</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-16,0; 2,12</t>
+          <t>-16,37; 1,51</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>126,18; 158,8</t>
+          <t>125,62; 161,3</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P3A_R-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P3A_R-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 30,66</t>
+          <t>0,07; 28,99</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-18,04; 13,52</t>
+          <t>-16,89; 14,26</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,45; 48,25</t>
+          <t>7,27; 48,54</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-16,44; 15,64</t>
+          <t>-14,01; 16,16</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-31,24; -0,23</t>
+          <t>-31,33; -0,99</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,75; 38,82</t>
+          <t>8,77; 40,55</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,96; 18,9</t>
+          <t>-3,07; 18,06</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-19,29; 2,04</t>
+          <t>-20,3; 2,19</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>14,0; 38,92</t>
+          <t>14,71; 39,89</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 101,69</t>
+          <t>0,08; 92,94</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-40,4; 43,7</t>
+          <t>-38,07; 45,06</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18,08; 151,89</t>
+          <t>21,18; 155,64</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-27,52; 38,64</t>
+          <t>-24,42; 39,66</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-55,27; 1,66</t>
+          <t>-55,65; -2,69</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,1; 100,36</t>
+          <t>15,78; 106,94</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-5,36; 51,67</t>
+          <t>-6,21; 46,63</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-40,73; 5,5</t>
+          <t>-42,99; 5,95</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>30,31; 103,05</t>
+          <t>28,9; 102,89</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-8,47; 3,84</t>
+          <t>-8,52; 3,75</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,96; 4,36</t>
+          <t>-8,24; 4,48</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>44,2; 55,2</t>
+          <t>43,7; 54,54</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-10,8; 0,94</t>
+          <t>-10,8; 1,01</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-9,63; 2,57</t>
+          <t>-10,04; 1,72</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>42,47; 52,49</t>
+          <t>42,5; 52,65</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-8,01; 0,56</t>
+          <t>-7,93; 0,73</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-7,16; 1,26</t>
+          <t>-7,32; 0,93</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>44,66; 52,12</t>
+          <t>44,92; 52,43</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-21,06; 11,24</t>
+          <t>-21,22; 11,26</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-19,85; 12,8</t>
+          <t>-20,31; 13,01</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>106,78; 166,07</t>
+          <t>104,38; 162,59</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-26,13; 2,67</t>
+          <t>-25,99; 2,28</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-23,11; 7,32</t>
+          <t>-23,81; 4,85</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,01; 148,53</t>
+          <t>100,28; 152,81</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-20,11; 1,57</t>
+          <t>-20,0; 1,64</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-18,16; 3,47</t>
+          <t>-18,01; 2,84</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>109,16; 146,82</t>
+          <t>109,46; 148,94</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-14,51; 3,68</t>
+          <t>-14,34; 3,57</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-13,47; 4,54</t>
+          <t>-14,52; 2,93</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>52,53; 67,67</t>
+          <t>51,22; 67,65</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,16; 14,67</t>
+          <t>-2,64; 15,36</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 15,01</t>
+          <t>-1,39; 16,2</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>61,71; 75,61</t>
+          <t>60,6; 75,07</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-5,77; 6,87</t>
+          <t>-6,26; 6,21</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-5,65; 6,89</t>
+          <t>-5,98; 6,74</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>57,99; 68,72</t>
+          <t>58,57; 68,97</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-43,27; 15,2</t>
+          <t>-43,71; 16,22</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-40,39; 17,58</t>
+          <t>-42,9; 11,57</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>149,98; 294,27</t>
+          <t>143,45; 287,65</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-12,12; 81,99</t>
+          <t>-10,67; 89,37</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-7,15; 87,77</t>
+          <t>-6,06; 90,92</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>220,87; 465,83</t>
+          <t>216,04; 453,55</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-19,71; 31,85</t>
+          <t>-22,29; 27,73</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-19,12; 30,93</t>
+          <t>-19,94; 29,48</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>193,44; 311,44</t>
+          <t>193,21; 314,3</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-5,96; 4,02</t>
+          <t>-6,15; 3,87</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-7,44; 2,15</t>
+          <t>-7,17; 2,15</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>46,16; 54,95</t>
+          <t>46,04; 55,45</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-7,0; 2,52</t>
+          <t>-6,69; 2,73</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-7,09; 2,08</t>
+          <t>-6,88; 2,56</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>46,52; 54,27</t>
+          <t>46,23; 54,45</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-4,86; 1,97</t>
+          <t>-4,78; 2,22</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-6,07; 0,52</t>
+          <t>-6,36; 0,38</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>47,25; 53,52</t>
+          <t>47,58; 53,53</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-15,9; 11,94</t>
+          <t>-16,22; 11,55</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-20,07; 6,49</t>
+          <t>-19,14; 6,48</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>120,3; 168,85</t>
+          <t>120,55; 173,73</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-18,68; 7,94</t>
+          <t>-17,66; 8,13</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-18,7; 6,28</t>
+          <t>-18,53; 7,6</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>121,04; 166,46</t>
+          <t>119,8; 167,91</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-12,96; 5,72</t>
+          <t>-12,91; 6,75</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-16,37; 1,51</t>
+          <t>-17,18; 1,16</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>125,62; 161,3</t>
+          <t>126,88; 160,71</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P3A_R-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P3A_R-Estudios-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-0,15</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-16,29</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>24,94</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>15,18</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>-2,13</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>31,99</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-0,15</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-16,29</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>24,46</t>
+          <t>41,78</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>28,55</t>
+          <t>33,28</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,07; 28,99</t>
+          <t>-14,76; 14,77</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-16,89; 14,26</t>
+          <t>-31,6; -1,35</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,27; 48,54</t>
+          <t>10,11; 39,57</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-14,01; 16,16</t>
+          <t>-1,72; 29,38</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-31,33; -0,99</t>
+          <t>-16,98; 15,11</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,77; 40,55</t>
+          <t>26,79; 56,24</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 18,06</t>
+          <t>-2,31; 18,23</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-20,3; 2,19</t>
+          <t>-20,59; 1,9</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>14,71; 39,89</t>
+          <t>22,11; 43,29</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-0,32%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-33,3%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>50,99%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>39,27%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>-5,51%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>82,76%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-0,32%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-33,3%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>50,01%</t>
+          <t>108,08%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>65,58%</t>
+          <t>76,44%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,08; 92,94</t>
+          <t>-27,79; 37,47</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-38,07; 45,06</t>
+          <t>-56,43; -2,4</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21,18; 155,64</t>
+          <t>17,84; 99,68</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-24,42; 39,66</t>
+          <t>-3,19; 93,02</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-55,65; -2,69</t>
+          <t>-37,12; 47,65</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,78; 106,94</t>
+          <t>55,73; 200,96</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-6,21; 46,63</t>
+          <t>-4,66; 48,02</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-42,99; 5,95</t>
+          <t>-42,36; 6,72</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>28,9; 102,89</t>
+          <t>45,0; 116,65</t>
         </is>
       </c>
     </row>
@@ -840,39 +840,39 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-5,17</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-3,94</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>47,16</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>-2,56</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>-1,93</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>49,35</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-5,17</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>48,92</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>-3,94</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>47,66</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-3,94</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
           <t>-2,99</t>
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>48,45</t>
+          <t>47,99</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-8,52; 3,75</t>
+          <t>-11,33; 0,73</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,24; 4,48</t>
+          <t>-10,2; 1,66</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>43,7; 54,54</t>
+          <t>42,15; 51,72</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-10,8; 1,01</t>
+          <t>-8,8; 3,31</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-10,04; 1,72</t>
+          <t>-7,94; 4,18</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>42,5; 52,65</t>
+          <t>43,21; 54,05</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-7,93; 0,73</t>
+          <t>-7,96; 0,59</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-7,32; 0,93</t>
+          <t>-7,2; 1,7</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>44,92; 52,43</t>
+          <t>44,13; 51,79</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-13,39%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-10,19%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>122,05%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>-6,83%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>-5,15%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>131,86%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-13,39%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-10,19%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>123,35%</t>
+          <t>130,71%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>127,26%</t>
+          <t>126,04%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-21,22; 11,26</t>
+          <t>-26,95; 2,4</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-20,31; 13,01</t>
+          <t>-24,4; 4,78</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>104,38; 162,59</t>
+          <t>98,86; 146,96</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-25,99; 2,28</t>
+          <t>-21,92; 9,81</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-23,81; 4,85</t>
+          <t>-19,66; 12,05</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>100,28; 152,81</t>
+          <t>103,59; 163,41</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-20,0; 1,64</t>
+          <t>-19,87; 1,61</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-18,01; 2,84</t>
+          <t>-17,86; 4,78</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>109,46; 148,94</t>
+          <t>108,37; 147,04</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>5,88</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>7,09</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>68,38</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>-5,52</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-5,56</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>59,81</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>5,88</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>7,09</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>68,36</t>
+          <t>59,97</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>63,95</t>
+          <t>64,01</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-14,34; 3,57</t>
+          <t>-3,06; 14,97</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-14,52; 2,93</t>
+          <t>-1,66; 15,86</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>51,22; 67,65</t>
+          <t>60,32; 74,85</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,64; 15,36</t>
+          <t>-14,35; 4,08</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 16,2</t>
+          <t>-13,5; 2,82</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>60,6; 75,07</t>
+          <t>52,18; 67,89</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-6,26; 6,21</t>
+          <t>-5,51; 8,35</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-5,98; 6,74</t>
+          <t>-6,16; 6,57</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>58,57; 68,97</t>
+          <t>58,62; 69,51</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>26,98%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>32,52%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>313,79%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>-18,8%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>-18,95%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>203,86%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>26,98%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>32,52%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>313,72%</t>
+          <t>204,39%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>248,3%</t>
+          <t>248,53%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-43,71; 16,22</t>
+          <t>-13,35; 85,76</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-42,9; 11,57</t>
+          <t>-8,46; 91,12</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>143,45; 287,65</t>
+          <t>210,94; 445,94</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-10,67; 89,37</t>
+          <t>-43,08; 16,97</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-6,06; 90,92</t>
+          <t>-40,89; 9,93</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>216,04; 453,55</t>
+          <t>150,11; 296,59</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-22,29; 27,73</t>
+          <t>-19,63; 39,39</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-19,94; 29,48</t>
+          <t>-20,75; 28,78</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>193,21; 314,3</t>
+          <t>197,36; 330,58</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-1,94</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-2,61</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>50,18</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>-1,0</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>-2,83</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>50,61</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-1,94</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-2,61</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>50,47</t>
+          <t>51,24</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>50,55</t>
+          <t>50,69</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,15; 3,87</t>
+          <t>-7,64; 2,28</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-7,17; 2,15</t>
+          <t>-7,6; 1,71</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>46,04; 55,45</t>
+          <t>45,66; 53,86</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-6,69; 2,73</t>
+          <t>-5,59; 4,2</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-6,88; 2,56</t>
+          <t>-7,89; 1,52</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>46,23; 54,45</t>
+          <t>46,88; 55,14</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-4,78; 2,22</t>
+          <t>-5,01; 1,99</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-6,36; 0,38</t>
+          <t>-5,93; 0,69</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>47,58; 53,53</t>
+          <t>47,85; 53,31</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-5,44%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-7,32%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>140,57%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>-2,83%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>-7,99%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>143,1%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-5,44%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-7,32%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>141,39%</t>
+          <t>144,88%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>142,23%</t>
+          <t>142,63%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-16,22; 11,55</t>
+          <t>-20,19; 6,92</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-19,14; 6,48</t>
+          <t>-19,78; 5,34</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>120,55; 173,73</t>
+          <t>117,16; 164,09</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-17,66; 8,13</t>
+          <t>-14,93; 12,82</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-18,53; 7,6</t>
+          <t>-21,13; 4,43</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>119,8; 167,91</t>
+          <t>120,59; 171,63</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-12,91; 6,75</t>
+          <t>-13,32; 6,01</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-17,18; 1,16</t>
+          <t>-16,0; 2,12</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>126,88; 160,71</t>
+          <t>126,91; 158,84</t>
         </is>
       </c>
     </row>
